--- a/docs/sample-output/04-warehouse/estimate.xlsx
+++ b/docs/sample-output/04-warehouse/estimate.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="722" uniqueCount="360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="728" uniqueCount="365">
   <si>
     <t>FINISHES SOLUTIONS</t>
   </si>
   <si>
-    <t>Total Project Cost — Summary   ·   I-20 Logistics Center — bulk warehouse · Total $47,315,978</t>
+    <t>Total Project Cost — Summary   ·   I-20 Logistics Center — bulk warehouse · Total $47,072,339</t>
   </si>
   <si>
     <t>COST SUMMARY</t>
@@ -90,7 +90,7 @@
     <t>Research data version</t>
   </si>
   <si>
-    <t>2026.7c60a42879</t>
+    <t>2026.0c737c8255</t>
   </si>
   <si>
     <t>Engine</t>
@@ -99,10 +99,10 @@
     <t>budget-engine-2.0.0</t>
   </si>
   <si>
-    <t>All defaults come from the research data shipped with the app (2026.7c60a42879), escalated to the construction midpoint and adjusted to the project location. Values marked "Derived estimate — verify" have no direct published source.</t>
-  </si>
-  <si>
-    <t>Cost by Component   ·   I-20 Logistics Center — bulk warehouse · Total $47,315,978</t>
+    <t>All defaults come from the research data shipped with the app (2026.0c737c8255), escalated to the construction midpoint and adjusted to the project location. Values marked "Derived estimate — verify" have no direct published source.</t>
+  </si>
+  <si>
+    <t>Cost by Component   ·   I-20 Logistics Center — bulk warehouse · Total $47,072,339</t>
   </si>
   <si>
     <t>Component</t>
@@ -147,7 +147,7 @@
     <t>within ($80–$230)</t>
   </si>
   <si>
-    <t>Cost by Phase   ·   I-20 Logistics Center — bulk warehouse · Total $47,315,978</t>
+    <t>Cost by Phase   ·   I-20 Logistics Center — bulk warehouse · Total $47,072,339</t>
   </si>
   <si>
     <t>Phase</t>
@@ -189,7 +189,7 @@
     <t>5.9%</t>
   </si>
   <si>
-    <t>Line-Item Detail   ·   I-20 Logistics Center — bulk warehouse · Total $47,315,978</t>
+    <t>Line-Item Detail   ·   I-20 Logistics Center — bulk warehouse · Total $47,072,339</t>
   </si>
   <si>
     <t>Group</t>
@@ -453,7 +453,7 @@
     <t>TOTAL</t>
   </si>
   <si>
-    <t>Draw Schedules   ·   I-20 Logistics Center — bulk warehouse · Total $47,315,978</t>
+    <t>Draw Schedules   ·   I-20 Logistics Center — bulk warehouse · Total $47,072,339</t>
   </si>
   <si>
     <t>PHASE 1 — MONTHLY DRAWS</t>
@@ -522,7 +522,7 @@
     <t>2028-09</t>
   </si>
   <si>
-    <t>Sources &amp; Assumptions   ·   I-20 Logistics Center — bulk warehouse · Total $47,315,978</t>
+    <t>Sources &amp; Assumptions   ·   I-20 Logistics Center — bulk warehouse · Total $47,072,339</t>
   </si>
   <si>
     <t>ASSUMPTIONS</t>
@@ -558,7 +558,7 @@
     <t>LTC 60%, rate 7.00%, fee 1.00%</t>
   </si>
   <si>
-    <t>SOURCES (49)</t>
+    <t>SOURCES (50)</t>
   </si>
   <si>
     <t>Ref</t>
@@ -1096,6 +1096,21 @@
   </si>
   <si>
     <t>85–170 USD/sf (2026)</t>
+  </si>
+  <si>
+    <t>residential/single-family.json#e10</t>
+  </si>
+  <si>
+    <t>Cost of Constructing a Home-2024 (Special Study for Housing Economics)</t>
+  </si>
+  <si>
+    <t>National Association of Home Builders (Eric Lynch)</t>
+  </si>
+  <si>
+    <t>26747 USD/unit (2024)</t>
+  </si>
+  <si>
+    <t>https://nahb.org/-/media/AB4EFC742624475A97A0A62189986FF8.ashx</t>
   </si>
 </sst>
 </file>
@@ -1685,7 +1700,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="5">
-        <v>4138491.6800000006</v>
+        <v>4138491.6799999997</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -1693,7 +1708,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="5">
-        <v>2106721.6</v>
+        <v>1897427.2</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -1701,7 +1716,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="5">
-        <v>1519540.72</v>
+        <v>1510582.92</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -1709,7 +1724,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="5">
-        <v>1409519.3</v>
+        <v>1398783.2</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -1717,7 +1732,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="5">
-        <v>429957.73</v>
+        <v>415307.12</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -1725,7 +1740,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="7">
-        <v>9604231.03</v>
+        <v>9360592.12</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -1741,7 +1756,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="7">
-        <v>47315978.11</v>
+        <v>47072339.2</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -1780,7 +1795,7 @@
         <v>22</v>
       </c>
       <c r="B21" s="5">
-        <v>1971499.0879166666</v>
+        <v>1961347.4666666668</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -1908,19 +1923,19 @@
         <v>31313347.08</v>
       </c>
       <c r="E5" s="13">
-        <v>9604231.03</v>
+        <v>9360592.12</v>
       </c>
       <c r="F5" s="13">
         <v>6398400</v>
       </c>
       <c r="G5" s="13">
-        <v>47315978.11</v>
+        <v>47072339.2</v>
       </c>
       <c r="H5" s="13">
-        <v>147.86243159375</v>
+        <v>147.10106000000002</v>
       </c>
       <c r="I5" s="14">
-        <v>147.86243159375</v>
+        <v>147.10106000000002</v>
       </c>
       <c r="J5" s="12" t="s">
         <v>42</v>
@@ -1936,13 +1951,13 @@
         <v>31313347.08</v>
       </c>
       <c r="E6" s="16">
-        <v>9604231.03</v>
+        <v>9360592.12</v>
       </c>
       <c r="F6" s="16">
         <v>6398400</v>
       </c>
       <c r="G6" s="16">
-        <v>47315978.11</v>
+        <v>47072339.2</v>
       </c>
       <c r="H6" s="15"/>
       <c r="I6" s="15"/>
@@ -2058,19 +2073,19 @@
         <v>31313347.08</v>
       </c>
       <c r="G5" s="13">
-        <v>9604231.03</v>
+        <v>9360592.12</v>
       </c>
       <c r="H5" s="13">
         <v>6398400</v>
       </c>
       <c r="I5" s="13">
-        <v>47315978.11</v>
+        <v>47072339.2</v>
       </c>
       <c r="J5" s="13">
-        <v>28389586.87</v>
+        <v>28243403.52</v>
       </c>
       <c r="K5" s="13">
-        <v>1125623.43</v>
+        <v>1116349.16</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
@@ -2085,13 +2100,13 @@
         <v>31313347.08</v>
       </c>
       <c r="G6" s="16">
-        <v>9604231.03</v>
+        <v>9360592.12</v>
       </c>
       <c r="H6" s="16">
         <v>6398400</v>
       </c>
       <c r="I6" s="16">
-        <v>47315978.11</v>
+        <v>47072339.2</v>
       </c>
       <c r="J6" s="15"/>
       <c r="K6" s="15"/>
@@ -3172,10 +3187,10 @@
         <v>129</v>
       </c>
       <c r="H38" s="14">
-        <v>4838.18</v>
+        <v>3407.22</v>
       </c>
       <c r="I38" s="13">
-        <v>387054.4</v>
+        <v>272577.6</v>
       </c>
       <c r="J38" s="12" t="s">
         <v>69</v>
@@ -3204,10 +3219,10 @@
         <v>129</v>
       </c>
       <c r="H39" s="14">
-        <v>4592.44</v>
+        <v>3407.22</v>
       </c>
       <c r="I39" s="13">
-        <v>367395.2</v>
+        <v>272577.6</v>
       </c>
       <c r="J39" s="12" t="s">
         <v>69</v>
@@ -3237,7 +3252,7 @@
       </c>
       <c r="H40" s="18"/>
       <c r="I40" s="13">
-        <v>429957.73</v>
+        <v>415307.12</v>
       </c>
       <c r="J40" s="12" t="s">
         <v>69</v>
@@ -3383,7 +3398,7 @@
       </c>
       <c r="H45" s="18"/>
       <c r="I45" s="13">
-        <v>1519540.72</v>
+        <v>1510582.92</v>
       </c>
       <c r="J45" s="12" t="s">
         <v>69</v>
@@ -3411,7 +3426,7 @@
       </c>
       <c r="H46" s="18"/>
       <c r="I46" s="13">
-        <v>1125623.43</v>
+        <v>1116349.16</v>
       </c>
       <c r="J46" s="12" t="s">
         <v>69</v>
@@ -3439,7 +3454,7 @@
       </c>
       <c r="H47" s="18"/>
       <c r="I47" s="13">
-        <v>283895.87</v>
+        <v>282434.04</v>
       </c>
       <c r="J47" s="12" t="s">
         <v>69</v>
@@ -3459,7 +3474,7 @@
       <c r="G48" s="15"/>
       <c r="H48" s="15"/>
       <c r="I48" s="16">
-        <v>47315978.11</v>
+        <v>47072339.2</v>
       </c>
       <c r="J48" s="15"/>
     </row>
@@ -3558,13 +3573,13 @@
         <v>0</v>
       </c>
       <c r="C6" s="13">
-        <v>4464538.56</v>
+        <v>4255244.16</v>
       </c>
       <c r="D6" s="13">
         <v>6398400</v>
       </c>
       <c r="E6" s="13">
-        <v>11146834.43</v>
+        <v>10936078.2</v>
       </c>
       <c r="F6" s="13">
         <v>0</v>
@@ -3584,13 +3599,13 @@
         <v>237860.05</v>
       </c>
       <c r="C7" s="13">
-        <v>207231.85</v>
+        <v>205920.27</v>
       </c>
       <c r="D7" s="13">
         <v>0</v>
       </c>
       <c r="E7" s="13">
-        <v>445091.9</v>
+        <v>443780.32</v>
       </c>
       <c r="F7" s="13">
         <v>0</v>
@@ -3610,13 +3625,13 @@
         <v>706352.88</v>
       </c>
       <c r="C8" s="13">
-        <v>207231.83</v>
+        <v>205920.25</v>
       </c>
       <c r="D8" s="13">
         <v>0</v>
       </c>
       <c r="E8" s="13">
-        <v>913584.71</v>
+        <v>912273.13</v>
       </c>
       <c r="F8" s="13">
         <v>0</v>
@@ -3636,13 +3651,13 @@
         <v>1153383.58</v>
       </c>
       <c r="C9" s="13">
-        <v>207231.83</v>
+        <v>205920.25</v>
       </c>
       <c r="D9" s="13">
         <v>0</v>
       </c>
       <c r="E9" s="13">
-        <v>1360615.41</v>
+        <v>1359303.83</v>
       </c>
       <c r="F9" s="13">
         <v>0</v>
@@ -3662,13 +3677,13 @@
         <v>1565369.25</v>
       </c>
       <c r="C10" s="13">
-        <v>207231.83</v>
+        <v>205920.25</v>
       </c>
       <c r="D10" s="13">
         <v>0</v>
       </c>
       <c r="E10" s="13">
-        <v>1772601.08</v>
+        <v>1771289.5</v>
       </c>
       <c r="F10" s="13">
         <v>0</v>
@@ -3688,13 +3703,13 @@
         <v>1929792.01</v>
       </c>
       <c r="C11" s="13">
-        <v>207231.88</v>
+        <v>205920.3</v>
       </c>
       <c r="D11" s="13">
         <v>0</v>
       </c>
       <c r="E11" s="13">
-        <v>2137023.89</v>
+        <v>2135712.31</v>
       </c>
       <c r="F11" s="13">
         <v>0</v>
@@ -3714,22 +3729,22 @@
         <v>2235578.98</v>
       </c>
       <c r="C12" s="13">
-        <v>207231.83</v>
+        <v>205920.24</v>
       </c>
       <c r="D12" s="13">
         <v>0</v>
       </c>
       <c r="E12" s="13">
-        <v>1150639.82</v>
+        <v>1270498.39</v>
       </c>
       <c r="F12" s="13">
-        <v>1292170.99</v>
+        <v>1171000.83</v>
       </c>
       <c r="G12" s="13">
         <v>0</v>
       </c>
       <c r="H12" s="13">
-        <v>1292170.99</v>
+        <v>1171000.83</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -3740,7 +3755,7 @@
         <v>2473439.05</v>
       </c>
       <c r="C13" s="13">
-        <v>207231.87</v>
+        <v>205920.3</v>
       </c>
       <c r="D13" s="13">
         <v>0</v>
@@ -3749,13 +3764,13 @@
         <v>0</v>
       </c>
       <c r="F13" s="13">
-        <v>2680670.92</v>
+        <v>2679359.35</v>
       </c>
       <c r="G13" s="13">
-        <v>7537.66</v>
+        <v>6830.84</v>
       </c>
       <c r="H13" s="13">
-        <v>3980379.57</v>
+        <v>3857191.02</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -3766,7 +3781,7 @@
         <v>2636144.88</v>
       </c>
       <c r="C14" s="13">
-        <v>207231.82</v>
+        <v>205920.23</v>
       </c>
       <c r="D14" s="13">
         <v>0</v>
@@ -3775,13 +3790,13 @@
         <v>0</v>
       </c>
       <c r="F14" s="13">
-        <v>2843376.7</v>
+        <v>2842065.11</v>
       </c>
       <c r="G14" s="13">
-        <v>23218.88</v>
+        <v>22500.28</v>
       </c>
       <c r="H14" s="13">
-        <v>6846975.15</v>
+        <v>6721756.41</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -3792,7 +3807,7 @@
         <v>2718752.82</v>
       </c>
       <c r="C15" s="13">
-        <v>207231.86</v>
+        <v>205920.29</v>
       </c>
       <c r="D15" s="13">
         <v>0</v>
@@ -3801,13 +3816,13 @@
         <v>0</v>
       </c>
       <c r="F15" s="13">
-        <v>2925984.68</v>
+        <v>2924673.11</v>
       </c>
       <c r="G15" s="13">
-        <v>39940.69</v>
+        <v>39210.25</v>
       </c>
       <c r="H15" s="13">
-        <v>9812900.52</v>
+        <v>9685639.77</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -3818,7 +3833,7 @@
         <v>2718752.85</v>
       </c>
       <c r="C16" s="13">
-        <v>207231.86</v>
+        <v>205920.29</v>
       </c>
       <c r="D16" s="13">
         <v>0</v>
@@ -3827,13 +3842,13 @@
         <v>0</v>
       </c>
       <c r="F16" s="13">
-        <v>2925984.71</v>
+        <v>2924673.14</v>
       </c>
       <c r="G16" s="13">
-        <v>57241.92</v>
+        <v>56499.57</v>
       </c>
       <c r="H16" s="13">
-        <v>12796127.15</v>
+        <v>12666812.48</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -3844,7 +3859,7 @@
         <v>2636144.88</v>
       </c>
       <c r="C17" s="13">
-        <v>207231.86</v>
+        <v>205920.29</v>
       </c>
       <c r="D17" s="13">
         <v>0</v>
@@ -3853,13 +3868,13 @@
         <v>0</v>
       </c>
       <c r="F17" s="13">
-        <v>2843376.74</v>
+        <v>2842065.17</v>
       </c>
       <c r="G17" s="13">
-        <v>74644.08</v>
+        <v>73889.74</v>
       </c>
       <c r="H17" s="13">
-        <v>15714147.97</v>
+        <v>15582767.39</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -3870,7 +3885,7 @@
         <v>2473439.04</v>
       </c>
       <c r="C18" s="13">
-        <v>207231.8</v>
+        <v>205920.22</v>
       </c>
       <c r="D18" s="13">
         <v>0</v>
@@ -3879,13 +3894,13 @@
         <v>0</v>
       </c>
       <c r="F18" s="13">
-        <v>2680670.84</v>
+        <v>2679359.26</v>
       </c>
       <c r="G18" s="13">
-        <v>91665.86</v>
+        <v>90899.48</v>
       </c>
       <c r="H18" s="13">
-        <v>18486484.67</v>
+        <v>18353026.13</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -3896,7 +3911,7 @@
         <v>2235579.02</v>
       </c>
       <c r="C19" s="13">
-        <v>207231.85</v>
+        <v>205920.28</v>
       </c>
       <c r="D19" s="13">
         <v>0</v>
@@ -3905,13 +3920,13 @@
         <v>0</v>
       </c>
       <c r="F19" s="13">
-        <v>2442810.87</v>
+        <v>2441499.3</v>
       </c>
       <c r="G19" s="13">
-        <v>107837.83</v>
+        <v>107059.32</v>
       </c>
       <c r="H19" s="13">
-        <v>21037133.37</v>
+        <v>20901584.75</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -3922,7 +3937,7 @@
         <v>1929792.01</v>
       </c>
       <c r="C20" s="13">
-        <v>207231.85</v>
+        <v>205920.27</v>
       </c>
       <c r="D20" s="13">
         <v>0</v>
@@ -3931,13 +3946,13 @@
         <v>0</v>
       </c>
       <c r="F20" s="13">
-        <v>2137023.86</v>
+        <v>2135712.28</v>
       </c>
       <c r="G20" s="13">
-        <v>122716.61</v>
+        <v>121925.91</v>
       </c>
       <c r="H20" s="13">
-        <v>23296873.84</v>
+        <v>23159222.94</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -3948,7 +3963,7 @@
         <v>1565369.27</v>
       </c>
       <c r="C21" s="13">
-        <v>207231.85</v>
+        <v>205920.27</v>
       </c>
       <c r="D21" s="13">
         <v>0</v>
@@ -3957,13 +3972,13 @@
         <v>0</v>
       </c>
       <c r="F21" s="13">
-        <v>1772601.12</v>
+        <v>1771289.54</v>
       </c>
       <c r="G21" s="13">
-        <v>135898.43</v>
+        <v>135095.47</v>
       </c>
       <c r="H21" s="13">
-        <v>25205373.39</v>
+        <v>25065607.95</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -3974,7 +3989,7 @@
         <v>1153383.57</v>
       </c>
       <c r="C22" s="13">
-        <v>207231.8</v>
+        <v>205920.22</v>
       </c>
       <c r="D22" s="13">
         <v>0</v>
@@ -3983,13 +3998,13 @@
         <v>0</v>
       </c>
       <c r="F22" s="13">
-        <v>1360615.37</v>
+        <v>1359303.79</v>
       </c>
       <c r="G22" s="13">
-        <v>147031.34</v>
+        <v>146216.05</v>
       </c>
       <c r="H22" s="13">
-        <v>26713020.1</v>
+        <v>26571127.79</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -4000,7 +4015,7 @@
         <v>706352.9</v>
       </c>
       <c r="C23" s="13">
-        <v>207231.85</v>
+        <v>205920.27</v>
       </c>
       <c r="D23" s="13">
         <v>0</v>
@@ -4009,13 +4024,13 @@
         <v>0</v>
       </c>
       <c r="F23" s="13">
-        <v>913584.75</v>
+        <v>912273.17</v>
       </c>
       <c r="G23" s="13">
-        <v>155825.95</v>
+        <v>154998.25</v>
       </c>
       <c r="H23" s="13">
-        <v>27782430.8</v>
+        <v>27638399.21</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -4026,7 +4041,7 @@
         <v>237860.04</v>
       </c>
       <c r="C24" s="13">
-        <v>207231.85</v>
+        <v>205920.27</v>
       </c>
       <c r="D24" s="13">
         <v>0</v>
@@ -4035,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="F24" s="13">
-        <v>445091.89</v>
+        <v>443780.31</v>
       </c>
       <c r="G24" s="13">
-        <v>162064.18</v>
+        <v>161224</v>
       </c>
       <c r="H24" s="13">
-        <v>28389586.87</v>
+        <v>28243403.52</v>
       </c>
     </row>
   </sheetData>
@@ -4063,7 +4078,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F60"/>
+  <dimension ref="A1:F61"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -5148,6 +5163,26 @@
       </c>
       <c r="F60" s="12" t="s">
         <v>333</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="11" t="s">
+        <v>360</v>
+      </c>
+      <c r="B61" s="12" t="s">
+        <v>361</v>
+      </c>
+      <c r="C61" s="12" t="s">
+        <v>362</v>
+      </c>
+      <c r="D61" s="12" t="s">
+        <v>363</v>
+      </c>
+      <c r="E61" s="12" t="s">
+        <v>205</v>
+      </c>
+      <c r="F61" s="12" t="s">
+        <v>364</v>
       </c>
     </row>
   </sheetData>
